--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Bank Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Bank Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="67">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Bank Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,24 +76,24 @@
     <t>INE090A01021</t>
   </si>
   <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
     <t>Kotak Mahindra Bank Ltd.</t>
   </si>
   <si>
     <t>INE237A01028</t>
   </si>
   <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>IndusInd Bank Ltd.</t>
   </si>
   <si>
@@ -118,24 +118,24 @@
     <t>INE092T01019</t>
   </si>
   <si>
+    <t>AU Small Finance Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE949L01017</t>
+  </si>
+  <si>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A01022</t>
+  </si>
+  <si>
     <t>Punjab National Bank</t>
   </si>
   <si>
     <t>INE160A01022</t>
   </si>
   <si>
-    <t>AU Small Finance Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE949L01017</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
-  </si>
-  <si>
-    <t>INE476A01022</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -184,6 +184,15 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t>Details of the Equity shares have been lent under Securities Lending and Borrowing as follows:-</t>
+  </si>
+  <si>
+    <t>Name of the Instrument</t>
+  </si>
+  <si>
+    <t>AU Small Finance Bank Ltd</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -193,7 +202,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -217,7 +226,7 @@
     <numFmt numFmtId="178" formatCode="##0.00%"/>
     <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -233,6 +242,18 @@
       <sz val="8.25"/>
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -293,7 +314,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -379,6 +400,20 @@
         <color auto="1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -405,44 +440,44 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -469,17 +504,35 @@
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -576,13 +629,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -600,7 +653,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="12268200"/>
+          <a:off x="666750" y="12839700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -615,13 +668,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -639,7 +692,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15125700"/>
+          <a:off x="666750" y="15697200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -973,19 +1026,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J76"/>
+  <dimension ref="B1:J79"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.142857142857142" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.142857142857142" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="19.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1073,10 +1126,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>52171.50</v>
+        <v>61523.75000000001</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9993476543229</v>
+        <v>0.9997105108332001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1110,10 +1163,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>52171.50</v>
+        <v>61523.75000000001</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9993476543229</v>
+        <v>0.9997105108332001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1136,13 +1189,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>848431</v>
+        <v>880003</v>
       </c>
       <c r="G8" s="15">
-        <v>14412.72</v>
+        <v>17115.18</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2760763620831</v>
+        <v>0.2781076468975</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1165,13 +1218,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>1043162</v>
+        <v>1071311</v>
       </c>
       <c r="G9" s="15">
-        <v>13068.73</v>
+        <v>15489.01</v>
       </c>
       <c r="H9" s="16">
-        <v>0.2503321673804</v>
+        <v>0.251683717254</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1194,13 +1247,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>263703</v>
+        <v>433710</v>
       </c>
       <c r="G10" s="15">
-        <v>5013.79</v>
+        <v>5170.69</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0960393946076</v>
+        <v>0.0840194744511</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1223,13 +1276,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>568936</v>
+        <v>627710</v>
       </c>
       <c r="G11" s="15">
-        <v>4397.31</v>
+        <v>5098.89</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0842306898178</v>
+        <v>0.0828527833005</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1252,13 +1305,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>429300</v>
+        <v>223559</v>
       </c>
       <c r="G12" s="15">
-        <v>4233.33</v>
+        <v>4638.18</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0810896448343</v>
+        <v>0.0753666234119</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1281,13 +1334,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>251506</v>
+        <v>301777</v>
       </c>
       <c r="G13" s="15">
-        <v>2492.93</v>
+        <v>2465.37</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0477521970403</v>
+        <v>0.0400602418105</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1310,13 +1363,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>931757</v>
+        <v>1123478</v>
       </c>
       <c r="G14" s="15">
-        <v>1744.34</v>
+        <v>2270.10</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0334129186882</v>
+        <v>0.0368872643595</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1339,13 +1392,13 @@
         <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>709308</v>
+        <v>848630</v>
       </c>
       <c r="G15" s="15">
-        <v>1513.59</v>
+        <v>2117.76</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0289928910632</v>
+        <v>0.0344118642219</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1368,13 +1421,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>2356651</v>
+        <v>2840955</v>
       </c>
       <c r="G16" s="15">
-        <v>1490.35</v>
+        <v>1931</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0285477277176</v>
+        <v>0.0313771672958</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1397,13 +1450,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>1311065</v>
+        <v>257235</v>
       </c>
       <c r="G17" s="15">
-        <v>1326.80</v>
+        <v>1782.77</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0254149194053</v>
+        <v>0.0289685512895</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1426,13 +1479,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="14">
-        <v>213321</v>
+        <v>1544855</v>
       </c>
       <c r="G18" s="15">
-        <v>1281.95</v>
+        <v>1772.88</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0245558154444</v>
+        <v>0.0288078468956</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1455,13 +1508,13 @@
         <v>17</v>
       </c>
       <c r="F19" s="14">
-        <v>1281937</v>
+        <v>1579964</v>
       </c>
       <c r="G19" s="15">
-        <v>1195.66</v>
+        <v>1671.92</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0229029262407</v>
+        <v>0.0271673296454</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1976,10 +2029,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="9">
-        <v>253.99</v>
+        <v>116.53</v>
       </c>
       <c r="H47" s="10">
-        <v>0.0048651909705</v>
+        <v>0.0018935169886</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>13</v>
@@ -2013,10 +2066,10 @@
         <v>13</v>
       </c>
       <c r="G49" s="18">
-        <v>-219.933931209991</v>
+        <v>-98.71438348000083</v>
       </c>
       <c r="H49" s="19">
-        <v>-0.004212845294094547</v>
+        <v>-0.001604027822352025</v>
       </c>
       <c r="I49" s="18" t="s">
         <v>13</v>
@@ -2042,10 +2095,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="18">
-        <v>52205.55606879</v>
+        <v>61541.56561652</v>
       </c>
       <c r="H50" s="19">
-        <v>0.9999999999993054</v>
+        <v>0.9999999999994479</v>
       </c>
       <c r="I50" s="18" t="s">
         <v>13</v>
@@ -2054,87 +2107,109 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="15" customHeight="1">
-      <c r="B53" s="13" t="s">
+    <row r="52" spans="2:3" ht="15" customHeight="1">
+      <c r="B52" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-    </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
-      <c r="B54" s="13" t="s">
+      <c r="C52" s="22"/>
+    </row>
+    <row r="53" spans="2:3" ht="15" customHeight="1">
+      <c r="B53" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-    </row>
-    <row r="55" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B55" s="22" t="s">
+      <c r="C53" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" ht="15" customHeight="1">
+      <c r="B54" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-    </row>
-    <row r="56" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B56" s="22" t="s">
+      <c r="C54" s="25">
+        <v>7322</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="15" customHeight="1">
+      <c r="B56" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-    </row>
-    <row r="57" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B57" s="22" t="s">
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+    </row>
+    <row r="57" spans="2:8" ht="15" customHeight="1">
+      <c r="B57" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-    </row>
-    <row r="60" ht="15">
-      <c r="B60" s="21" t="s">
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+    </row>
+    <row r="58" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B58" s="27" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="75" ht="15">
-      <c r="B75" s="21" t="s">
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+    </row>
+    <row r="59" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B59" s="27" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="76" ht="15">
-      <c r="B76" s="21" t="s">
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+    </row>
+    <row r="60" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B60" s="27" t="s">
         <v>63</v>
+      </c>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+    </row>
+    <row r="63" ht="15">
+      <c r="B63" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" ht="15">
+      <c r="B78" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" ht="15">
+      <c r="B79" s="26" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B56:H56"/>
-    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B60:H60"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B53:I53"/>
-    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:H57"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
